--- a/input/defects/欠陥一覧_運用.xlsx
+++ b/input/defects/欠陥一覧_運用.xlsx
@@ -16,20 +16,16 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="1">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
-    <numFmt numFmtId="165" formatCode="YYYY/MM/DD"/>
   </numFmts>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -40,7 +36,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -48,25 +44,13 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -432,283 +416,274 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A10:G24"/>
+  <dimension ref="B10:H20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
-  </cols>
   <sheetData>
     <row r="10">
-      <c r="A10" s="1" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>No.</t>
         </is>
       </c>
-      <c r="B10" s="1" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>日付</t>
         </is>
       </c>
-      <c r="C10" s="1" t="inlineStr">
+      <c r="D10" t="inlineStr">
         <is>
           <t>検出欠陥数</t>
         </is>
       </c>
-      <c r="D10" s="1" t="inlineStr">
+      <c r="E10" t="inlineStr">
         <is>
           <t>対応欠陥数</t>
         </is>
       </c>
-      <c r="E10" s="1" t="inlineStr">
+      <c r="F10" t="inlineStr">
         <is>
           <t>累積検出欠陥数</t>
         </is>
       </c>
-      <c r="F10" s="1" t="inlineStr">
+      <c r="G10" t="inlineStr">
         <is>
           <t>累積対応欠陥数</t>
         </is>
       </c>
-      <c r="G10" s="1" t="inlineStr">
+      <c r="H10" t="inlineStr">
         <is>
           <t>累積未対応欠陥数</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="n">
+      <c r="B11" t="n">
         <v>1</v>
       </c>
-      <c r="B11" s="3" t="n">
+      <c r="C11" s="1" t="n">
         <v>46077</v>
       </c>
-      <c r="C11" s="2" t="n">
+      <c r="D11" t="n">
+        <v>5</v>
+      </c>
+      <c r="E11" t="n">
         <v>0</v>
       </c>
-      <c r="D11" s="2" t="n">
+      <c r="F11" t="n">
+        <v>5</v>
+      </c>
+      <c r="G11" t="n">
         <v>0</v>
       </c>
-      <c r="E11" s="2" t="n">
+      <c r="H11" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" t="n">
+        <v>2</v>
+      </c>
+      <c r="C12" s="1" t="n">
+        <v>46078</v>
+      </c>
+      <c r="D12" t="n">
+        <v>5</v>
+      </c>
+      <c r="E12" t="n">
         <v>0</v>
       </c>
-      <c r="F11" s="2" t="n">
+      <c r="F12" t="n">
+        <v>10</v>
+      </c>
+      <c r="G12" t="n">
         <v>0</v>
       </c>
-      <c r="G11" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="n">
+      <c r="H12" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" t="n">
+        <v>3</v>
+      </c>
+      <c r="C13" s="1" t="n">
+        <v>46079</v>
+      </c>
+      <c r="D13" t="n">
+        <v>5</v>
+      </c>
+      <c r="E13" t="n">
+        <v>3</v>
+      </c>
+      <c r="F13" t="n">
+        <v>15</v>
+      </c>
+      <c r="G13" t="n">
+        <v>3</v>
+      </c>
+      <c r="H13" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" t="n">
+        <v>4</v>
+      </c>
+      <c r="C14" s="1" t="n">
+        <v>46080</v>
+      </c>
+      <c r="D14" t="n">
+        <v>4</v>
+      </c>
+      <c r="E14" t="n">
+        <v>3</v>
+      </c>
+      <c r="F14" t="n">
+        <v>19</v>
+      </c>
+      <c r="G14" t="n">
+        <v>6</v>
+      </c>
+      <c r="H14" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" t="n">
+        <v>5</v>
+      </c>
+      <c r="C15" s="1" t="n">
+        <v>46081</v>
+      </c>
+      <c r="D15" t="n">
+        <v>4</v>
+      </c>
+      <c r="E15" t="n">
+        <v>3</v>
+      </c>
+      <c r="F15" t="n">
+        <v>23</v>
+      </c>
+      <c r="G15" t="n">
+        <v>9</v>
+      </c>
+      <c r="H15" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" t="n">
+        <v>6</v>
+      </c>
+      <c r="C16" s="1" t="n">
+        <v>46082</v>
+      </c>
+      <c r="D16" t="n">
+        <v>4</v>
+      </c>
+      <c r="E16" t="n">
+        <v>3</v>
+      </c>
+      <c r="F16" t="n">
+        <v>27</v>
+      </c>
+      <c r="G16" t="n">
+        <v>12</v>
+      </c>
+      <c r="H16" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" t="n">
+        <v>7</v>
+      </c>
+      <c r="C17" s="1" t="n">
+        <v>46083</v>
+      </c>
+      <c r="D17" t="n">
+        <v>3</v>
+      </c>
+      <c r="E17" t="n">
+        <v>3</v>
+      </c>
+      <c r="F17" t="n">
+        <v>30</v>
+      </c>
+      <c r="G17" t="n">
+        <v>15</v>
+      </c>
+      <c r="H17" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" t="n">
+        <v>8</v>
+      </c>
+      <c r="C18" s="1" t="n">
+        <v>46084</v>
+      </c>
+      <c r="D18" t="n">
+        <v>3</v>
+      </c>
+      <c r="E18" t="n">
+        <v>3</v>
+      </c>
+      <c r="F18" t="n">
+        <v>33</v>
+      </c>
+      <c r="G18" t="n">
+        <v>18</v>
+      </c>
+      <c r="H18" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" t="n">
+        <v>9</v>
+      </c>
+      <c r="C19" s="1" t="n">
+        <v>46085</v>
+      </c>
+      <c r="D19" t="n">
+        <v>3</v>
+      </c>
+      <c r="E19" t="n">
+        <v>3</v>
+      </c>
+      <c r="F19" t="n">
+        <v>36</v>
+      </c>
+      <c r="G19" t="n">
+        <v>21</v>
+      </c>
+      <c r="H19" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" t="n">
+        <v>10</v>
+      </c>
+      <c r="C20" s="1" t="n">
+        <v>46086</v>
+      </c>
+      <c r="D20" t="n">
         <v>2</v>
       </c>
-      <c r="B12" s="3" t="n">
-        <v>46078</v>
-      </c>
-      <c r="C12" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="D12" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="E12" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F12" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G12" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="B13" s="3" t="n">
-        <v>46079</v>
-      </c>
-      <c r="C13" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="D13" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="E13" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="F13" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="G13" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="B14" s="3" t="n">
-        <v>46080</v>
-      </c>
-      <c r="C14" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D14" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E14" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="F14" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="G14" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="B17" s="3" t="n">
-        <v>46083</v>
-      </c>
-      <c r="C17" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="D17" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E17" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="F17" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="G17" s="2" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="B18" s="3" t="n">
-        <v>46084</v>
-      </c>
-      <c r="C18" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="D18" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="E18" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="F18" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="G18" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="B19" s="3" t="n">
-        <v>46085</v>
-      </c>
-      <c r="C19" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D19" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E19" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="F19" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="G19" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="B20" s="3" t="n">
-        <v>46086</v>
-      </c>
-      <c r="C20" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D20" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E20" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="F20" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="G20" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="B21" s="3" t="n">
-        <v>46087</v>
-      </c>
-      <c r="C21" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="D21" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="E21" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="F21" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="G21" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="2" t="n">
+      <c r="E20" t="n">
+        <v>3</v>
+      </c>
+      <c r="F20" t="n">
+        <v>38</v>
+      </c>
+      <c r="G20" t="n">
+        <v>24</v>
+      </c>
+      <c r="H20" t="n">
         <v>14</v>
-      </c>
-      <c r="B24" s="3" t="n">
-        <v>46090</v>
-      </c>
-      <c r="C24" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="D24" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E24" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="F24" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="G24" s="2" t="n">
-        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/input/defects/欠陥一覧_運用.xlsx
+++ b/input/defects/欠陥一覧_運用.xlsx
@@ -8,6 +8,7 @@
   </bookViews>
   <sheets>
     <sheet name="欠陥発見・対応推移集計表" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="テスト欠陥一覧" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -16,16 +17,20 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
+    <numFmt numFmtId="165" formatCode="YYYY/MM/DD"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -48,9 +53,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -416,43 +424,43 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B10:H20"/>
+  <dimension ref="B10:H79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="10">
-      <c r="B10" t="inlineStr">
+      <c r="B10" s="1" t="inlineStr">
         <is>
           <t>No.</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C10" s="1" t="inlineStr">
         <is>
           <t>日付</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>検出欠陥数</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>対応欠陥数</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>累積検出欠陥数</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>累積対応欠陥数</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>累積未対応欠陥数</t>
+      <c r="D10" s="1" t="inlineStr">
+        <is>
+          <t>検出</t>
+        </is>
+      </c>
+      <c r="E10" s="1" t="inlineStr">
+        <is>
+          <t>対応</t>
+        </is>
+      </c>
+      <c r="F10" s="1" t="inlineStr">
+        <is>
+          <t>累積検出</t>
+        </is>
+      </c>
+      <c r="G10" s="1" t="inlineStr">
+        <is>
+          <t>累積対応</t>
+        </is>
+      </c>
+      <c r="H10" s="1" t="inlineStr">
+        <is>
+          <t>累積未対応</t>
         </is>
       </c>
     </row>
@@ -460,230 +468,3059 @@
       <c r="B11" t="n">
         <v>1</v>
       </c>
-      <c r="C11" s="1" t="n">
-        <v>46077</v>
+      <c r="C11" s="2" t="n">
+        <v>45992</v>
       </c>
       <c r="D11" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
       <c r="B12" t="n">
         <v>2</v>
       </c>
-      <c r="C12" s="1" t="n">
-        <v>46078</v>
+      <c r="C12" s="2" t="n">
+        <v>45993</v>
       </c>
       <c r="D12" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
       <c r="B13" t="n">
         <v>3</v>
       </c>
-      <c r="C13" s="1" t="n">
-        <v>46079</v>
+      <c r="C13" s="2" t="n">
+        <v>45994</v>
       </c>
       <c r="D13" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E13" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="G13" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14">
       <c r="B14" t="n">
         <v>4</v>
       </c>
-      <c r="C14" s="1" t="n">
-        <v>46080</v>
+      <c r="C14" s="2" t="n">
+        <v>45995</v>
       </c>
       <c r="D14" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E14" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F14" t="n">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="G14" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="H14" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
       <c r="B15" t="n">
         <v>5</v>
       </c>
-      <c r="C15" s="1" t="n">
-        <v>46081</v>
+      <c r="C15" s="2" t="n">
+        <v>45996</v>
       </c>
       <c r="D15" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" t="n">
         <v>3</v>
       </c>
-      <c r="F15" t="n">
-        <v>23</v>
-      </c>
       <c r="G15" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="H15" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16">
       <c r="B16" t="n">
         <v>6</v>
       </c>
-      <c r="C16" s="1" t="n">
-        <v>46082</v>
+      <c r="C16" s="2" t="n">
+        <v>45999</v>
       </c>
       <c r="D16" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" t="n">
         <v>3</v>
       </c>
-      <c r="F16" t="n">
-        <v>27</v>
-      </c>
       <c r="G16" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="H16" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
     </row>
     <row r="17">
       <c r="B17" t="n">
         <v>7</v>
       </c>
-      <c r="C17" s="1" t="n">
-        <v>46083</v>
+      <c r="C17" s="2" t="n">
+        <v>46000</v>
       </c>
       <c r="D17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E17" t="n">
+        <v>1</v>
+      </c>
+      <c r="F17" t="n">
         <v>3</v>
       </c>
-      <c r="E17" t="n">
-        <v>3</v>
-      </c>
-      <c r="F17" t="n">
-        <v>30</v>
-      </c>
       <c r="G17" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="H17" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18">
       <c r="B18" t="n">
         <v>8</v>
       </c>
-      <c r="C18" s="1" t="n">
-        <v>46084</v>
+      <c r="C18" s="2" t="n">
+        <v>46001</v>
       </c>
       <c r="D18" t="n">
+        <v>0</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" t="n">
         <v>3</v>
       </c>
-      <c r="E18" t="n">
-        <v>3</v>
-      </c>
-      <c r="F18" t="n">
-        <v>33</v>
-      </c>
       <c r="G18" t="n">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="H18" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19">
       <c r="B19" t="n">
         <v>9</v>
       </c>
-      <c r="C19" s="1" t="n">
-        <v>46085</v>
+      <c r="C19" s="2" t="n">
+        <v>46002</v>
       </c>
       <c r="D19" t="n">
+        <v>0</v>
+      </c>
+      <c r="E19" t="n">
+        <v>1</v>
+      </c>
+      <c r="F19" t="n">
         <v>3</v>
       </c>
-      <c r="E19" t="n">
+      <c r="G19" t="n">
         <v>3</v>
       </c>
-      <c r="F19" t="n">
-        <v>36</v>
-      </c>
-      <c r="G19" t="n">
-        <v>21</v>
-      </c>
       <c r="H19" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="B20" t="n">
         <v>10</v>
       </c>
-      <c r="C20" s="1" t="n">
+      <c r="C20" s="2" t="n">
+        <v>46003</v>
+      </c>
+      <c r="D20" t="n">
+        <v>1</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" t="n">
+        <v>4</v>
+      </c>
+      <c r="G20" t="n">
+        <v>3</v>
+      </c>
+      <c r="H20" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" t="n">
+        <v>11</v>
+      </c>
+      <c r="C21" s="2" t="n">
+        <v>46006</v>
+      </c>
+      <c r="D21" t="n">
+        <v>1</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" t="n">
+        <v>5</v>
+      </c>
+      <c r="G21" t="n">
+        <v>3</v>
+      </c>
+      <c r="H21" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" t="n">
+        <v>12</v>
+      </c>
+      <c r="C22" s="2" t="n">
+        <v>46007</v>
+      </c>
+      <c r="D22" t="n">
+        <v>2</v>
+      </c>
+      <c r="E22" t="n">
+        <v>0</v>
+      </c>
+      <c r="F22" t="n">
+        <v>7</v>
+      </c>
+      <c r="G22" t="n">
+        <v>3</v>
+      </c>
+      <c r="H22" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" t="n">
+        <v>13</v>
+      </c>
+      <c r="C23" s="2" t="n">
+        <v>46008</v>
+      </c>
+      <c r="D23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E23" t="n">
+        <v>1</v>
+      </c>
+      <c r="F23" t="n">
+        <v>7</v>
+      </c>
+      <c r="G23" t="n">
+        <v>4</v>
+      </c>
+      <c r="H23" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" t="n">
+        <v>14</v>
+      </c>
+      <c r="C24" s="2" t="n">
+        <v>46009</v>
+      </c>
+      <c r="D24" t="n">
+        <v>1</v>
+      </c>
+      <c r="E24" t="n">
+        <v>1</v>
+      </c>
+      <c r="F24" t="n">
+        <v>8</v>
+      </c>
+      <c r="G24" t="n">
+        <v>5</v>
+      </c>
+      <c r="H24" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" t="n">
+        <v>15</v>
+      </c>
+      <c r="C25" s="2" t="n">
+        <v>46010</v>
+      </c>
+      <c r="D25" t="n">
+        <v>0</v>
+      </c>
+      <c r="E25" t="n">
+        <v>1</v>
+      </c>
+      <c r="F25" t="n">
+        <v>8</v>
+      </c>
+      <c r="G25" t="n">
+        <v>6</v>
+      </c>
+      <c r="H25" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" t="n">
+        <v>16</v>
+      </c>
+      <c r="C26" s="2" t="n">
+        <v>46013</v>
+      </c>
+      <c r="D26" t="n">
+        <v>0</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0</v>
+      </c>
+      <c r="F26" t="n">
+        <v>8</v>
+      </c>
+      <c r="G26" t="n">
+        <v>6</v>
+      </c>
+      <c r="H26" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" t="n">
+        <v>17</v>
+      </c>
+      <c r="C27" s="2" t="n">
+        <v>46014</v>
+      </c>
+      <c r="D27" t="n">
+        <v>1</v>
+      </c>
+      <c r="E27" t="n">
+        <v>1</v>
+      </c>
+      <c r="F27" t="n">
+        <v>9</v>
+      </c>
+      <c r="G27" t="n">
+        <v>7</v>
+      </c>
+      <c r="H27" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="B28" t="n">
+        <v>18</v>
+      </c>
+      <c r="C28" s="2" t="n">
+        <v>46015</v>
+      </c>
+      <c r="D28" t="n">
+        <v>0</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0</v>
+      </c>
+      <c r="F28" t="n">
+        <v>9</v>
+      </c>
+      <c r="G28" t="n">
+        <v>7</v>
+      </c>
+      <c r="H28" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" t="n">
+        <v>19</v>
+      </c>
+      <c r="C29" s="2" t="n">
+        <v>46016</v>
+      </c>
+      <c r="D29" t="n">
+        <v>0</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0</v>
+      </c>
+      <c r="F29" t="n">
+        <v>9</v>
+      </c>
+      <c r="G29" t="n">
+        <v>7</v>
+      </c>
+      <c r="H29" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="B30" t="n">
+        <v>20</v>
+      </c>
+      <c r="C30" s="2" t="n">
+        <v>46017</v>
+      </c>
+      <c r="D30" t="n">
+        <v>0</v>
+      </c>
+      <c r="E30" t="n">
+        <v>1</v>
+      </c>
+      <c r="F30" t="n">
+        <v>9</v>
+      </c>
+      <c r="G30" t="n">
+        <v>8</v>
+      </c>
+      <c r="H30" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="B31" t="n">
+        <v>21</v>
+      </c>
+      <c r="C31" s="2" t="n">
+        <v>46020</v>
+      </c>
+      <c r="D31" t="n">
+        <v>1</v>
+      </c>
+      <c r="E31" t="n">
+        <v>1</v>
+      </c>
+      <c r="F31" t="n">
+        <v>10</v>
+      </c>
+      <c r="G31" t="n">
+        <v>9</v>
+      </c>
+      <c r="H31" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" t="n">
+        <v>22</v>
+      </c>
+      <c r="C32" s="2" t="n">
+        <v>46021</v>
+      </c>
+      <c r="D32" t="n">
+        <v>0</v>
+      </c>
+      <c r="E32" t="n">
+        <v>1</v>
+      </c>
+      <c r="F32" t="n">
+        <v>10</v>
+      </c>
+      <c r="G32" t="n">
+        <v>10</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="B33" t="n">
+        <v>23</v>
+      </c>
+      <c r="C33" s="2" t="n">
+        <v>46022</v>
+      </c>
+      <c r="D33" t="n">
+        <v>1</v>
+      </c>
+      <c r="E33" t="n">
+        <v>0</v>
+      </c>
+      <c r="F33" t="n">
+        <v>11</v>
+      </c>
+      <c r="G33" t="n">
+        <v>10</v>
+      </c>
+      <c r="H33" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="B34" t="n">
+        <v>24</v>
+      </c>
+      <c r="C34" s="2" t="n">
+        <v>46023</v>
+      </c>
+      <c r="D34" t="n">
+        <v>0</v>
+      </c>
+      <c r="E34" t="n">
+        <v>1</v>
+      </c>
+      <c r="F34" t="n">
+        <v>11</v>
+      </c>
+      <c r="G34" t="n">
+        <v>11</v>
+      </c>
+      <c r="H34" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="B35" t="n">
+        <v>25</v>
+      </c>
+      <c r="C35" s="2" t="n">
+        <v>46024</v>
+      </c>
+      <c r="D35" t="n">
+        <v>0</v>
+      </c>
+      <c r="E35" t="n">
+        <v>0</v>
+      </c>
+      <c r="F35" t="n">
+        <v>11</v>
+      </c>
+      <c r="G35" t="n">
+        <v>11</v>
+      </c>
+      <c r="H35" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="B36" t="n">
+        <v>26</v>
+      </c>
+      <c r="C36" s="2" t="n">
+        <v>46027</v>
+      </c>
+      <c r="D36" t="n">
+        <v>0</v>
+      </c>
+      <c r="E36" t="n">
+        <v>0</v>
+      </c>
+      <c r="F36" t="n">
+        <v>11</v>
+      </c>
+      <c r="G36" t="n">
+        <v>11</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="B37" t="n">
+        <v>27</v>
+      </c>
+      <c r="C37" s="2" t="n">
+        <v>46028</v>
+      </c>
+      <c r="D37" t="n">
+        <v>0</v>
+      </c>
+      <c r="E37" t="n">
+        <v>0</v>
+      </c>
+      <c r="F37" t="n">
+        <v>11</v>
+      </c>
+      <c r="G37" t="n">
+        <v>11</v>
+      </c>
+      <c r="H37" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="B38" t="n">
+        <v>28</v>
+      </c>
+      <c r="C38" s="2" t="n">
+        <v>46029</v>
+      </c>
+      <c r="D38" t="n">
+        <v>0</v>
+      </c>
+      <c r="E38" t="n">
+        <v>0</v>
+      </c>
+      <c r="F38" t="n">
+        <v>11</v>
+      </c>
+      <c r="G38" t="n">
+        <v>11</v>
+      </c>
+      <c r="H38" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="B39" t="n">
+        <v>29</v>
+      </c>
+      <c r="C39" s="2" t="n">
+        <v>46030</v>
+      </c>
+      <c r="D39" t="n">
+        <v>2</v>
+      </c>
+      <c r="E39" t="n">
+        <v>0</v>
+      </c>
+      <c r="F39" t="n">
+        <v>13</v>
+      </c>
+      <c r="G39" t="n">
+        <v>11</v>
+      </c>
+      <c r="H39" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="B40" t="n">
+        <v>30</v>
+      </c>
+      <c r="C40" s="2" t="n">
+        <v>46031</v>
+      </c>
+      <c r="D40" t="n">
+        <v>1</v>
+      </c>
+      <c r="E40" t="n">
+        <v>0</v>
+      </c>
+      <c r="F40" t="n">
+        <v>14</v>
+      </c>
+      <c r="G40" t="n">
+        <v>11</v>
+      </c>
+      <c r="H40" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="B41" t="n">
+        <v>31</v>
+      </c>
+      <c r="C41" s="2" t="n">
+        <v>46034</v>
+      </c>
+      <c r="D41" t="n">
+        <v>0</v>
+      </c>
+      <c r="E41" t="n">
+        <v>1</v>
+      </c>
+      <c r="F41" t="n">
+        <v>14</v>
+      </c>
+      <c r="G41" t="n">
+        <v>12</v>
+      </c>
+      <c r="H41" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="B42" t="n">
+        <v>32</v>
+      </c>
+      <c r="C42" s="2" t="n">
+        <v>46035</v>
+      </c>
+      <c r="D42" t="n">
+        <v>0</v>
+      </c>
+      <c r="E42" t="n">
+        <v>0</v>
+      </c>
+      <c r="F42" t="n">
+        <v>14</v>
+      </c>
+      <c r="G42" t="n">
+        <v>12</v>
+      </c>
+      <c r="H42" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="B43" t="n">
+        <v>33</v>
+      </c>
+      <c r="C43" s="2" t="n">
+        <v>46036</v>
+      </c>
+      <c r="D43" t="n">
+        <v>0</v>
+      </c>
+      <c r="E43" t="n">
+        <v>1</v>
+      </c>
+      <c r="F43" t="n">
+        <v>14</v>
+      </c>
+      <c r="G43" t="n">
+        <v>13</v>
+      </c>
+      <c r="H43" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="B44" t="n">
+        <v>34</v>
+      </c>
+      <c r="C44" s="2" t="n">
+        <v>46037</v>
+      </c>
+      <c r="D44" t="n">
+        <v>0</v>
+      </c>
+      <c r="E44" t="n">
+        <v>1</v>
+      </c>
+      <c r="F44" t="n">
+        <v>14</v>
+      </c>
+      <c r="G44" t="n">
+        <v>14</v>
+      </c>
+      <c r="H44" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="B45" t="n">
+        <v>35</v>
+      </c>
+      <c r="C45" s="2" t="n">
+        <v>46038</v>
+      </c>
+      <c r="D45" t="n">
+        <v>0</v>
+      </c>
+      <c r="E45" t="n">
+        <v>0</v>
+      </c>
+      <c r="F45" t="n">
+        <v>14</v>
+      </c>
+      <c r="G45" t="n">
+        <v>14</v>
+      </c>
+      <c r="H45" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="B46" t="n">
+        <v>36</v>
+      </c>
+      <c r="C46" s="2" t="n">
+        <v>46041</v>
+      </c>
+      <c r="D46" t="n">
+        <v>1</v>
+      </c>
+      <c r="E46" t="n">
+        <v>0</v>
+      </c>
+      <c r="F46" t="n">
+        <v>15</v>
+      </c>
+      <c r="G46" t="n">
+        <v>14</v>
+      </c>
+      <c r="H46" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="B47" t="n">
+        <v>37</v>
+      </c>
+      <c r="C47" s="2" t="n">
+        <v>46042</v>
+      </c>
+      <c r="D47" t="n">
+        <v>0</v>
+      </c>
+      <c r="E47" t="n">
+        <v>0</v>
+      </c>
+      <c r="F47" t="n">
+        <v>15</v>
+      </c>
+      <c r="G47" t="n">
+        <v>14</v>
+      </c>
+      <c r="H47" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="B48" t="n">
+        <v>38</v>
+      </c>
+      <c r="C48" s="2" t="n">
+        <v>46043</v>
+      </c>
+      <c r="D48" t="n">
+        <v>0</v>
+      </c>
+      <c r="E48" t="n">
+        <v>1</v>
+      </c>
+      <c r="F48" t="n">
+        <v>15</v>
+      </c>
+      <c r="G48" t="n">
+        <v>15</v>
+      </c>
+      <c r="H48" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="B49" t="n">
+        <v>39</v>
+      </c>
+      <c r="C49" s="2" t="n">
+        <v>46044</v>
+      </c>
+      <c r="D49" t="n">
+        <v>2</v>
+      </c>
+      <c r="E49" t="n">
+        <v>0</v>
+      </c>
+      <c r="F49" t="n">
+        <v>17</v>
+      </c>
+      <c r="G49" t="n">
+        <v>15</v>
+      </c>
+      <c r="H49" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="B50" t="n">
+        <v>40</v>
+      </c>
+      <c r="C50" s="2" t="n">
+        <v>46045</v>
+      </c>
+      <c r="D50" t="n">
+        <v>0</v>
+      </c>
+      <c r="E50" t="n">
+        <v>0</v>
+      </c>
+      <c r="F50" t="n">
+        <v>17</v>
+      </c>
+      <c r="G50" t="n">
+        <v>15</v>
+      </c>
+      <c r="H50" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="B51" t="n">
+        <v>41</v>
+      </c>
+      <c r="C51" s="2" t="n">
+        <v>46048</v>
+      </c>
+      <c r="D51" t="n">
+        <v>2</v>
+      </c>
+      <c r="E51" t="n">
+        <v>0</v>
+      </c>
+      <c r="F51" t="n">
+        <v>19</v>
+      </c>
+      <c r="G51" t="n">
+        <v>15</v>
+      </c>
+      <c r="H51" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="B52" t="n">
+        <v>42</v>
+      </c>
+      <c r="C52" s="2" t="n">
+        <v>46049</v>
+      </c>
+      <c r="D52" t="n">
+        <v>0</v>
+      </c>
+      <c r="E52" t="n">
+        <v>1</v>
+      </c>
+      <c r="F52" t="n">
+        <v>19</v>
+      </c>
+      <c r="G52" t="n">
+        <v>16</v>
+      </c>
+      <c r="H52" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="B53" t="n">
+        <v>43</v>
+      </c>
+      <c r="C53" s="2" t="n">
+        <v>46050</v>
+      </c>
+      <c r="D53" t="n">
+        <v>0</v>
+      </c>
+      <c r="E53" t="n">
+        <v>1</v>
+      </c>
+      <c r="F53" t="n">
+        <v>19</v>
+      </c>
+      <c r="G53" t="n">
+        <v>17</v>
+      </c>
+      <c r="H53" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="B54" t="n">
+        <v>44</v>
+      </c>
+      <c r="C54" s="2" t="n">
+        <v>46051</v>
+      </c>
+      <c r="D54" t="n">
+        <v>1</v>
+      </c>
+      <c r="E54" t="n">
+        <v>1</v>
+      </c>
+      <c r="F54" t="n">
+        <v>20</v>
+      </c>
+      <c r="G54" t="n">
+        <v>18</v>
+      </c>
+      <c r="H54" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="B55" t="n">
+        <v>45</v>
+      </c>
+      <c r="C55" s="2" t="n">
+        <v>46052</v>
+      </c>
+      <c r="D55" t="n">
+        <v>2</v>
+      </c>
+      <c r="E55" t="n">
+        <v>0</v>
+      </c>
+      <c r="F55" t="n">
+        <v>22</v>
+      </c>
+      <c r="G55" t="n">
+        <v>18</v>
+      </c>
+      <c r="H55" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="B56" t="n">
+        <v>46</v>
+      </c>
+      <c r="C56" s="2" t="n">
+        <v>46055</v>
+      </c>
+      <c r="D56" t="n">
+        <v>1</v>
+      </c>
+      <c r="E56" t="n">
+        <v>0</v>
+      </c>
+      <c r="F56" t="n">
+        <v>23</v>
+      </c>
+      <c r="G56" t="n">
+        <v>18</v>
+      </c>
+      <c r="H56" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="B57" t="n">
+        <v>47</v>
+      </c>
+      <c r="C57" s="2" t="n">
+        <v>46056</v>
+      </c>
+      <c r="D57" t="n">
+        <v>2</v>
+      </c>
+      <c r="E57" t="n">
+        <v>1</v>
+      </c>
+      <c r="F57" t="n">
+        <v>25</v>
+      </c>
+      <c r="G57" t="n">
+        <v>19</v>
+      </c>
+      <c r="H57" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="B58" t="n">
+        <v>48</v>
+      </c>
+      <c r="C58" s="2" t="n">
+        <v>46057</v>
+      </c>
+      <c r="D58" t="n">
+        <v>0</v>
+      </c>
+      <c r="E58" t="n">
+        <v>1</v>
+      </c>
+      <c r="F58" t="n">
+        <v>25</v>
+      </c>
+      <c r="G58" t="n">
+        <v>20</v>
+      </c>
+      <c r="H58" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="B59" t="n">
+        <v>49</v>
+      </c>
+      <c r="C59" s="2" t="n">
+        <v>46058</v>
+      </c>
+      <c r="D59" t="n">
+        <v>0</v>
+      </c>
+      <c r="E59" t="n">
+        <v>1</v>
+      </c>
+      <c r="F59" t="n">
+        <v>25</v>
+      </c>
+      <c r="G59" t="n">
+        <v>21</v>
+      </c>
+      <c r="H59" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="B60" t="n">
+        <v>50</v>
+      </c>
+      <c r="C60" s="2" t="n">
+        <v>46059</v>
+      </c>
+      <c r="D60" t="n">
+        <v>2</v>
+      </c>
+      <c r="E60" t="n">
+        <v>1</v>
+      </c>
+      <c r="F60" t="n">
+        <v>27</v>
+      </c>
+      <c r="G60" t="n">
+        <v>22</v>
+      </c>
+      <c r="H60" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="B61" t="n">
+        <v>51</v>
+      </c>
+      <c r="C61" s="2" t="n">
+        <v>46062</v>
+      </c>
+      <c r="D61" t="n">
+        <v>0</v>
+      </c>
+      <c r="E61" t="n">
+        <v>1</v>
+      </c>
+      <c r="F61" t="n">
+        <v>27</v>
+      </c>
+      <c r="G61" t="n">
+        <v>23</v>
+      </c>
+      <c r="H61" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="B62" t="n">
+        <v>52</v>
+      </c>
+      <c r="C62" s="2" t="n">
+        <v>46063</v>
+      </c>
+      <c r="D62" t="n">
+        <v>1</v>
+      </c>
+      <c r="E62" t="n">
+        <v>1</v>
+      </c>
+      <c r="F62" t="n">
+        <v>28</v>
+      </c>
+      <c r="G62" t="n">
+        <v>24</v>
+      </c>
+      <c r="H62" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="B63" t="n">
+        <v>53</v>
+      </c>
+      <c r="C63" s="2" t="n">
+        <v>46064</v>
+      </c>
+      <c r="D63" t="n">
+        <v>0</v>
+      </c>
+      <c r="E63" t="n">
+        <v>1</v>
+      </c>
+      <c r="F63" t="n">
+        <v>28</v>
+      </c>
+      <c r="G63" t="n">
+        <v>25</v>
+      </c>
+      <c r="H63" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="B64" t="n">
+        <v>54</v>
+      </c>
+      <c r="C64" s="2" t="n">
+        <v>46065</v>
+      </c>
+      <c r="D64" t="n">
+        <v>0</v>
+      </c>
+      <c r="E64" t="n">
+        <v>0</v>
+      </c>
+      <c r="F64" t="n">
+        <v>28</v>
+      </c>
+      <c r="G64" t="n">
+        <v>25</v>
+      </c>
+      <c r="H64" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="B65" t="n">
+        <v>55</v>
+      </c>
+      <c r="C65" s="2" t="n">
+        <v>46066</v>
+      </c>
+      <c r="D65" t="n">
+        <v>1</v>
+      </c>
+      <c r="E65" t="n">
+        <v>0</v>
+      </c>
+      <c r="F65" t="n">
+        <v>29</v>
+      </c>
+      <c r="G65" t="n">
+        <v>25</v>
+      </c>
+      <c r="H65" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="B66" t="n">
+        <v>56</v>
+      </c>
+      <c r="C66" s="2" t="n">
+        <v>46069</v>
+      </c>
+      <c r="D66" t="n">
+        <v>0</v>
+      </c>
+      <c r="E66" t="n">
+        <v>1</v>
+      </c>
+      <c r="F66" t="n">
+        <v>29</v>
+      </c>
+      <c r="G66" t="n">
+        <v>26</v>
+      </c>
+      <c r="H66" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="B67" t="n">
+        <v>57</v>
+      </c>
+      <c r="C67" s="2" t="n">
+        <v>46070</v>
+      </c>
+      <c r="D67" t="n">
+        <v>0</v>
+      </c>
+      <c r="E67" t="n">
+        <v>1</v>
+      </c>
+      <c r="F67" t="n">
+        <v>29</v>
+      </c>
+      <c r="G67" t="n">
+        <v>27</v>
+      </c>
+      <c r="H67" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="B68" t="n">
+        <v>58</v>
+      </c>
+      <c r="C68" s="2" t="n">
+        <v>46071</v>
+      </c>
+      <c r="D68" t="n">
+        <v>0</v>
+      </c>
+      <c r="E68" t="n">
+        <v>0</v>
+      </c>
+      <c r="F68" t="n">
+        <v>29</v>
+      </c>
+      <c r="G68" t="n">
+        <v>27</v>
+      </c>
+      <c r="H68" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="B69" t="n">
+        <v>59</v>
+      </c>
+      <c r="C69" s="2" t="n">
+        <v>46072</v>
+      </c>
+      <c r="D69" t="n">
+        <v>0</v>
+      </c>
+      <c r="E69" t="n">
+        <v>1</v>
+      </c>
+      <c r="F69" t="n">
+        <v>29</v>
+      </c>
+      <c r="G69" t="n">
+        <v>28</v>
+      </c>
+      <c r="H69" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="B70" t="n">
+        <v>60</v>
+      </c>
+      <c r="C70" s="2" t="n">
+        <v>46073</v>
+      </c>
+      <c r="D70" t="n">
+        <v>0</v>
+      </c>
+      <c r="E70" t="n">
+        <v>0</v>
+      </c>
+      <c r="F70" t="n">
+        <v>29</v>
+      </c>
+      <c r="G70" t="n">
+        <v>28</v>
+      </c>
+      <c r="H70" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="B71" t="n">
+        <v>61</v>
+      </c>
+      <c r="C71" s="2" t="n">
+        <v>46076</v>
+      </c>
+      <c r="D71" t="n">
+        <v>0</v>
+      </c>
+      <c r="E71" t="n">
+        <v>0</v>
+      </c>
+      <c r="F71" t="n">
+        <v>29</v>
+      </c>
+      <c r="G71" t="n">
+        <v>28</v>
+      </c>
+      <c r="H71" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="B72" t="n">
+        <v>62</v>
+      </c>
+      <c r="C72" s="2" t="n">
+        <v>46077</v>
+      </c>
+      <c r="D72" t="n">
+        <v>0</v>
+      </c>
+      <c r="E72" t="n">
+        <v>0</v>
+      </c>
+      <c r="F72" t="n">
+        <v>29</v>
+      </c>
+      <c r="G72" t="n">
+        <v>28</v>
+      </c>
+      <c r="H72" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="B73" t="n">
+        <v>63</v>
+      </c>
+      <c r="C73" s="2" t="n">
+        <v>46078</v>
+      </c>
+      <c r="D73" t="n">
+        <v>0</v>
+      </c>
+      <c r="E73" t="n">
+        <v>1</v>
+      </c>
+      <c r="F73" t="n">
+        <v>29</v>
+      </c>
+      <c r="G73" t="n">
+        <v>29</v>
+      </c>
+      <c r="H73" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="B74" t="n">
+        <v>64</v>
+      </c>
+      <c r="C74" s="2" t="n">
+        <v>46079</v>
+      </c>
+      <c r="D74" t="n">
+        <v>0</v>
+      </c>
+      <c r="E74" t="n">
+        <v>0</v>
+      </c>
+      <c r="F74" t="n">
+        <v>29</v>
+      </c>
+      <c r="G74" t="n">
+        <v>29</v>
+      </c>
+      <c r="H74" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="B75" t="n">
+        <v>65</v>
+      </c>
+      <c r="C75" s="2" t="n">
+        <v>46080</v>
+      </c>
+      <c r="D75" t="n">
+        <v>0</v>
+      </c>
+      <c r="E75" t="n">
+        <v>0</v>
+      </c>
+      <c r="F75" t="n">
+        <v>29</v>
+      </c>
+      <c r="G75" t="n">
+        <v>29</v>
+      </c>
+      <c r="H75" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="B76" t="n">
+        <v>66</v>
+      </c>
+      <c r="C76" s="2" t="n">
+        <v>46083</v>
+      </c>
+      <c r="D76" t="n">
+        <v>0</v>
+      </c>
+      <c r="E76" t="n">
+        <v>0</v>
+      </c>
+      <c r="F76" t="n">
+        <v>29</v>
+      </c>
+      <c r="G76" t="n">
+        <v>29</v>
+      </c>
+      <c r="H76" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="B77" t="n">
+        <v>67</v>
+      </c>
+      <c r="C77" s="2" t="n">
+        <v>46084</v>
+      </c>
+      <c r="D77" t="n">
+        <v>0</v>
+      </c>
+      <c r="E77" t="n">
+        <v>0</v>
+      </c>
+      <c r="F77" t="n">
+        <v>29</v>
+      </c>
+      <c r="G77" t="n">
+        <v>29</v>
+      </c>
+      <c r="H77" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="B78" t="n">
+        <v>68</v>
+      </c>
+      <c r="C78" s="2" t="n">
+        <v>46085</v>
+      </c>
+      <c r="D78" t="n">
+        <v>1</v>
+      </c>
+      <c r="E78" t="n">
+        <v>0</v>
+      </c>
+      <c r="F78" t="n">
+        <v>30</v>
+      </c>
+      <c r="G78" t="n">
+        <v>29</v>
+      </c>
+      <c r="H78" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="B79" t="n">
+        <v>69</v>
+      </c>
+      <c r="C79" s="2" t="n">
         <v>46086</v>
       </c>
-      <c r="D20" t="n">
-        <v>2</v>
-      </c>
-      <c r="E20" t="n">
-        <v>3</v>
-      </c>
-      <c r="F20" t="n">
-        <v>38</v>
-      </c>
-      <c r="G20" t="n">
-        <v>24</v>
-      </c>
-      <c r="H20" t="n">
-        <v>14</v>
+      <c r="D79" t="n">
+        <v>0</v>
+      </c>
+      <c r="E79" t="n">
+        <v>0</v>
+      </c>
+      <c r="F79" t="n">
+        <v>30</v>
+      </c>
+      <c r="G79" t="n">
+        <v>29</v>
+      </c>
+      <c r="H79" t="n">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A8:AP26"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>欠陥ID</t>
+        </is>
+      </c>
+      <c r="B8" s="1" t="inlineStr">
+        <is>
+          <t>対応状況</t>
+        </is>
+      </c>
+      <c r="C8" s="1" t="inlineStr">
+        <is>
+          <t>件名</t>
+        </is>
+      </c>
+      <c r="D8" s="1" t="inlineStr">
+        <is>
+          <t>発見日</t>
+        </is>
+      </c>
+      <c r="G8" s="1" t="inlineStr">
+        <is>
+          <t>業務機能分類</t>
+        </is>
+      </c>
+      <c r="M8" s="1" t="inlineStr">
+        <is>
+          <t>緊急度</t>
+        </is>
+      </c>
+      <c r="N8" s="1" t="inlineStr">
+        <is>
+          <t>影響度</t>
+        </is>
+      </c>
+      <c r="O8" s="1" t="inlineStr">
+        <is>
+          <t>調査予定日</t>
+        </is>
+      </c>
+      <c r="P8" s="1" t="inlineStr">
+        <is>
+          <t>調査完了日</t>
+        </is>
+      </c>
+      <c r="T8" s="1" t="inlineStr">
+        <is>
+          <t>欠陥原因（深層）</t>
+        </is>
+      </c>
+      <c r="U8" s="1" t="inlineStr">
+        <is>
+          <t>欠陥埋込フェーズ</t>
+        </is>
+      </c>
+      <c r="V8" s="1" t="inlineStr">
+        <is>
+          <t>検出すべきフェーズ</t>
+        </is>
+      </c>
+      <c r="AD8" s="1" t="inlineStr">
+        <is>
+          <t>対応予定日</t>
+        </is>
+      </c>
+      <c r="AE8" s="1" t="inlineStr">
+        <is>
+          <t>対応日</t>
+        </is>
+      </c>
+      <c r="AG8" s="1" t="inlineStr">
+        <is>
+          <t>横展開有無</t>
+        </is>
+      </c>
+      <c r="AH8" s="1" t="inlineStr">
+        <is>
+          <t>横展開先</t>
+        </is>
+      </c>
+      <c r="AI8" s="1" t="inlineStr">
+        <is>
+          <t>横展開完了予定日</t>
+        </is>
+      </c>
+      <c r="AJ8" s="1" t="inlineStr">
+        <is>
+          <t>横展開完了日</t>
+        </is>
+      </c>
+      <c r="AK8" s="1" t="inlineStr">
+        <is>
+          <t>リリース予定日</t>
+        </is>
+      </c>
+      <c r="AL8" s="1" t="inlineStr">
+        <is>
+          <t>リリース日</t>
+        </is>
+      </c>
+      <c r="AM8" s="1" t="inlineStr">
+        <is>
+          <t>検証日</t>
+        </is>
+      </c>
+      <c r="AP8" s="1" t="inlineStr">
+        <is>
+          <t>集計フラグ</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>DEF-運-0001</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>05:完了</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>欠陥1: 03_請求の不具合</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="n">
+        <v>46047</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>02_受付</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="O9" s="2" t="n">
+        <v>46049</v>
+      </c>
+      <c r="P9" s="2" t="n">
+        <v>46051</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>プロセス不備</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>その他</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>非欠陥</t>
+        </is>
+      </c>
+      <c r="AD9" s="2" t="n">
+        <v>46059</v>
+      </c>
+      <c r="AE9" s="2" t="n">
+        <v>46057</v>
+      </c>
+      <c r="AG9" t="inlineStr">
+        <is>
+          <t>無</t>
+        </is>
+      </c>
+      <c r="AH9" t="inlineStr"/>
+      <c r="AK9" s="2" t="n">
+        <v>46064</v>
+      </c>
+      <c r="AL9" s="2" t="n">
+        <v>46064</v>
+      </c>
+      <c r="AM9" s="2" t="n">
+        <v>46059</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>DEF-運-0002</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>05:完了</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>欠陥2: 02_受付の不具合</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="n">
+        <v>46011</v>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>06_受入準備</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="n">
+        <v>46016</v>
+      </c>
+      <c r="P10" s="2" t="n">
+        <v>46015</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>非欠陥</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>ED</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>CT</t>
+        </is>
+      </c>
+      <c r="AD10" s="2" t="n">
+        <v>46019</v>
+      </c>
+      <c r="AE10" s="2" t="n">
+        <v>46017</v>
+      </c>
+      <c r="AG10" t="inlineStr">
+        <is>
+          <t>無</t>
+        </is>
+      </c>
+      <c r="AH10" t="inlineStr"/>
+      <c r="AK10" s="2" t="n">
+        <v>46025</v>
+      </c>
+      <c r="AL10" s="2" t="n">
+        <v>46028</v>
+      </c>
+      <c r="AM10" s="2" t="n">
+        <v>46021</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>DEF-運-0003</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>05:完了</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>欠陥3: 10_共通の不具合</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="n">
+        <v>46017</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>03_請求</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="n">
+        <v>46022</v>
+      </c>
+      <c r="P11" s="2" t="n">
+        <v>46021</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>考慮不足</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>その他</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>CT</t>
+        </is>
+      </c>
+      <c r="AD11" s="2" t="n">
+        <v>46029</v>
+      </c>
+      <c r="AE11" s="2" t="n">
+        <v>46033</v>
+      </c>
+      <c r="AG11" t="inlineStr">
+        <is>
+          <t>無</t>
+        </is>
+      </c>
+      <c r="AH11" t="inlineStr"/>
+      <c r="AK11" s="2" t="n">
+        <v>46037</v>
+      </c>
+      <c r="AL11" s="2" t="n">
+        <v>46038</v>
+      </c>
+      <c r="AM11" s="2" t="n">
+        <v>46038</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>DEF-運-0004</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>05:完了</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>欠陥4: 05_清算の不具合</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="n">
+        <v>46059</v>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>01_委託者登録</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="n">
+        <v>46062</v>
+      </c>
+      <c r="P12" s="2" t="n">
+        <v>46064</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>技術力不足</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>RD</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>非欠陥</t>
+        </is>
+      </c>
+      <c r="AD12" s="2" t="n">
+        <v>46070</v>
+      </c>
+      <c r="AE12" s="2" t="n">
+        <v>46075</v>
+      </c>
+      <c r="AG12" t="inlineStr">
+        <is>
+          <t>無</t>
+        </is>
+      </c>
+      <c r="AH12" t="inlineStr"/>
+      <c r="AK12" s="2" t="n">
+        <v>46083</v>
+      </c>
+      <c r="AL12" s="2" t="n">
+        <v>46082</v>
+      </c>
+      <c r="AM12" s="2" t="n">
+        <v>46077</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>DEF-運-0005</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>05:完了</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>欠陥5: 05_清算の不具合</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="n">
+        <v>46005</v>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>03_請求</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="n">
+        <v>46007</v>
+      </c>
+      <c r="P13" s="2" t="n">
+        <v>46007</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>非欠陥</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>ED</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>CT</t>
+        </is>
+      </c>
+      <c r="AD13" s="2" t="n">
+        <v>46010</v>
+      </c>
+      <c r="AE13" s="2" t="n">
+        <v>46015</v>
+      </c>
+      <c r="AG13" t="inlineStr">
+        <is>
+          <t>有</t>
+        </is>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>20_移行</t>
+        </is>
+      </c>
+      <c r="AI13" s="2" t="n">
+        <v>46015</v>
+      </c>
+      <c r="AJ13" s="2" t="n">
+        <v>46017</v>
+      </c>
+      <c r="AK13" s="2" t="n">
+        <v>46022</v>
+      </c>
+      <c r="AL13" s="2" t="n">
+        <v>46021</v>
+      </c>
+      <c r="AM13" s="2" t="n">
+        <v>46017</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>DEF-運-0006</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>04:検証中</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>欠陥6: 40_基盤の不具合</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="n">
+        <v>46028</v>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>05_清算</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="n">
+        <v>46032</v>
+      </c>
+      <c r="P14" s="2" t="n">
+        <v>46034</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>情報共有不足</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>非欠陥</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>ITb</t>
+        </is>
+      </c>
+      <c r="AD14" s="2" t="n">
+        <v>46041</v>
+      </c>
+      <c r="AE14" s="2" t="n">
+        <v>46041</v>
+      </c>
+      <c r="AG14" t="inlineStr">
+        <is>
+          <t>有</t>
+        </is>
+      </c>
+      <c r="AH14" t="inlineStr">
+        <is>
+          <t>30_運用</t>
+        </is>
+      </c>
+      <c r="AI14" s="2" t="n">
+        <v>46046</v>
+      </c>
+      <c r="AK14" s="2" t="n">
+        <v>46052</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>DEF-運-0007</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>04:検証中</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>欠陥7: 06_受入準備の不具合</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="n">
+        <v>46009</v>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>30_運用</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="O15" s="2" t="n">
+        <v>46014</v>
+      </c>
+      <c r="P15" s="2" t="n">
+        <v>46017</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>プロセス不備</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>その他</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>ITb</t>
+        </is>
+      </c>
+      <c r="AD15" s="2" t="n">
+        <v>46023</v>
+      </c>
+      <c r="AE15" s="2" t="n">
+        <v>46026</v>
+      </c>
+      <c r="AG15" t="inlineStr">
+        <is>
+          <t>有</t>
+        </is>
+      </c>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>30_運用</t>
+        </is>
+      </c>
+      <c r="AI15" s="2" t="n">
+        <v>46029</v>
+      </c>
+      <c r="AK15" s="2" t="n">
+        <v>46034</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>DEF-運-0008</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>04:検証中</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>欠陥8: 40_基盤の不具合</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="n">
+        <v>46079</v>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>08_事務支(変更通知)</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="n">
+        <v>46081</v>
+      </c>
+      <c r="P16" s="2" t="n">
+        <v>46080</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>注意不足</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>非欠陥</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>ITa</t>
+        </is>
+      </c>
+      <c r="AD16" s="2" t="n">
+        <v>46088</v>
+      </c>
+      <c r="AE16" s="2" t="n">
+        <v>46089</v>
+      </c>
+      <c r="AG16" t="inlineStr">
+        <is>
+          <t>無</t>
+        </is>
+      </c>
+      <c r="AH16" t="inlineStr"/>
+      <c r="AK16" s="2" t="n">
+        <v>46093</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>DEF-運-0009</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>03:対応中</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>欠陥9: 40_基盤の不具合</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="n">
+        <v>45998</v>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>06_受入準備</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="n">
+        <v>46002</v>
+      </c>
+      <c r="P17" s="2" t="n">
+        <v>46002</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>影響範囲調査不足</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>ITb</t>
+        </is>
+      </c>
+      <c r="AD17" s="2" t="n">
+        <v>46006</v>
+      </c>
+      <c r="AG17" t="inlineStr">
+        <is>
+          <t>無</t>
+        </is>
+      </c>
+      <c r="AH17" t="inlineStr"/>
+      <c r="AK17" s="2" t="n">
+        <v>46014</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>DEF-運-0010</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>03:対応中</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>欠陥10: 02_受付の不具合</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="n">
+        <v>46062</v>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>06_受入準備</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="O18" s="2" t="n">
+        <v>46072</v>
+      </c>
+      <c r="P18" s="2" t="n">
+        <v>46075</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>非欠陥</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>非欠陥</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="AD18" s="2" t="n">
+        <v>46076</v>
+      </c>
+      <c r="AG18" t="inlineStr">
+        <is>
+          <t>無</t>
+        </is>
+      </c>
+      <c r="AH18" t="inlineStr"/>
+      <c r="AK18" s="2" t="n">
+        <v>46085</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>DEF-運-0011</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>02:調査中</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>欠陥11: 03_請求の不具合</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="n">
+        <v>46011</v>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>06_受入準備</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="n">
+        <v>46014</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>業務/仕様理解不足</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>PD</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>非欠陥</t>
+        </is>
+      </c>
+      <c r="AD19" s="2" t="n">
+        <v>46018</v>
+      </c>
+      <c r="AG19" t="inlineStr">
+        <is>
+          <t>無</t>
+        </is>
+      </c>
+      <c r="AH19" t="inlineStr"/>
+      <c r="AK19" s="2" t="n">
+        <v>46031</v>
+      </c>
+      <c r="AP19" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>DEF-運-0012</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>02:調査中</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>欠陥12: 30_運用の不具合</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="n">
+        <v>46066</v>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>20_移行</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="n">
+        <v>46071</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>PD</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>非欠陥</t>
+        </is>
+      </c>
+      <c r="AD20" s="2" t="n">
+        <v>46078</v>
+      </c>
+      <c r="AG20" t="inlineStr">
+        <is>
+          <t>無</t>
+        </is>
+      </c>
+      <c r="AH20" t="inlineStr"/>
+      <c r="AK20" s="2" t="n">
+        <v>46084</v>
+      </c>
+      <c r="AP20" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>DEF-運-0013</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>01:未着手</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>欠陥13: 01_委託者登録の不具合</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="n">
+        <v>46071</v>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>08_事務支(変更通知)</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="O21" s="2" t="n">
+        <v>46073</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>その他</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>非欠陥</t>
+        </is>
+      </c>
+      <c r="AD21" s="2" t="n">
+        <v>46076</v>
+      </c>
+      <c r="AG21" t="inlineStr">
+        <is>
+          <t>無</t>
+        </is>
+      </c>
+      <c r="AH21" t="inlineStr"/>
+      <c r="AK21" s="2" t="n">
+        <v>46081</v>
+      </c>
+      <c r="AP21" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>DEF-運-0014</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>01:未着手</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>欠陥14: 40_基盤の不具合</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="n">
+        <v>46003</v>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>08_事務支(変更通知)</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="n">
+        <v>46006</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>注意不足</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>PD</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="AD22" s="2" t="n">
+        <v>46009</v>
+      </c>
+      <c r="AG22" t="inlineStr">
+        <is>
+          <t>無</t>
+        </is>
+      </c>
+      <c r="AH22" t="inlineStr"/>
+      <c r="AK22" s="2" t="n">
+        <v>46016</v>
+      </c>
+      <c r="AP22" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>DEF-運-0015</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>98:保留</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>欠陥15: 03_請求の不具合</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="n">
+        <v>46035</v>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>07_口振契約受付</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="O23" s="2" t="n">
+        <v>46037</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>考慮不足</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>CT</t>
+        </is>
+      </c>
+      <c r="AD23" s="2" t="n">
+        <v>46040</v>
+      </c>
+      <c r="AG23" t="inlineStr">
+        <is>
+          <t>無</t>
+        </is>
+      </c>
+      <c r="AH23" t="inlineStr"/>
+      <c r="AK23" s="2" t="n">
+        <v>46046</v>
+      </c>
+      <c r="AP23" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>DEF-運-0016</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>98:保留</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>欠陥16: 07_口振契約受付の不具合</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="n">
+        <v>45998</v>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>20_移行</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="O24" s="2" t="n">
+        <v>45999</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>注意不足</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>ED</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>ITa</t>
+        </is>
+      </c>
+      <c r="AD24" s="2" t="n">
+        <v>46003</v>
+      </c>
+      <c r="AG24" t="inlineStr">
+        <is>
+          <t>有</t>
+        </is>
+      </c>
+      <c r="AH24" t="inlineStr">
+        <is>
+          <t>30_運用</t>
+        </is>
+      </c>
+      <c r="AI24" s="2" t="n">
+        <v>46010</v>
+      </c>
+      <c r="AK24" s="2" t="n">
+        <v>46010</v>
+      </c>
+      <c r="AP24" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>DEF-運-0017</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>99:対応無し</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>欠陥17: 04_欠陥・返戻の不具合</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="n">
+        <v>46046</v>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>01_委託者登録</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="O25" s="2" t="n">
+        <v>46047</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>プロセス不備</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>非欠陥</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>ITb</t>
+        </is>
+      </c>
+      <c r="AD25" s="2" t="n">
+        <v>46050</v>
+      </c>
+      <c r="AG25" t="inlineStr">
+        <is>
+          <t>無</t>
+        </is>
+      </c>
+      <c r="AH25" t="inlineStr"/>
+      <c r="AK25" s="2" t="n">
+        <v>46056</v>
+      </c>
+      <c r="AP25" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>DEF-運-0018</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>99:対応無し</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>欠陥18: 09_事務支(その他)の不具合</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="n">
+        <v>45996</v>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>07_口振契約受付</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="O26" s="2" t="n">
+        <v>46000</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>外的要因</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="AD26" s="2" t="n">
+        <v>46008</v>
+      </c>
+      <c r="AG26" t="inlineStr">
+        <is>
+          <t>有</t>
+        </is>
+      </c>
+      <c r="AH26" t="inlineStr">
+        <is>
+          <t>02_受付</t>
+        </is>
+      </c>
+      <c r="AI26" s="2" t="n">
+        <v>46012</v>
+      </c>
+      <c r="AK26" s="2" t="n">
+        <v>46016</v>
+      </c>
+      <c r="AP26" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/input/defects/欠陥一覧_運用.xlsx
+++ b/input/defects/欠陥一覧_運用.xlsx
@@ -53,12 +53,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -495,19 +496,19 @@
         <v>45993</v>
       </c>
       <c r="D12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13">
@@ -518,7 +519,7 @@
         <v>45994</v>
       </c>
       <c r="D13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -564,19 +565,19 @@
         <v>45996</v>
       </c>
       <c r="D15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G15" t="n">
         <v>1</v>
       </c>
       <c r="H15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -587,19 +588,19 @@
         <v>45999</v>
       </c>
       <c r="D16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G16" t="n">
         <v>1</v>
       </c>
       <c r="H16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17">
@@ -613,13 +614,13 @@
         <v>0</v>
       </c>
       <c r="E17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F17" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H17" t="n">
         <v>1</v>
@@ -639,10 +640,10 @@
         <v>0</v>
       </c>
       <c r="F18" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H18" t="n">
         <v>1</v>
@@ -662,10 +663,10 @@
         <v>1</v>
       </c>
       <c r="F19" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G19" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H19" t="n">
         <v>0</v>
@@ -679,7 +680,7 @@
         <v>46003</v>
       </c>
       <c r="D20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
@@ -688,10 +689,10 @@
         <v>4</v>
       </c>
       <c r="G20" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="21">
@@ -702,19 +703,19 @@
         <v>46006</v>
       </c>
       <c r="D21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F21" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G21" t="n">
         <v>3</v>
       </c>
       <c r="H21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22">
@@ -725,19 +726,19 @@
         <v>46007</v>
       </c>
       <c r="D22" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F22" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="G22" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H22" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -751,16 +752,16 @@
         <v>0</v>
       </c>
       <c r="E23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F23" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="G23" t="n">
         <v>4</v>
       </c>
       <c r="H23" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -771,19 +772,19 @@
         <v>46009</v>
       </c>
       <c r="D24" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F24" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G24" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H24" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="25">
@@ -797,13 +798,13 @@
         <v>0</v>
       </c>
       <c r="E25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F25" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G25" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H25" t="n">
         <v>2</v>
@@ -823,10 +824,10 @@
         <v>0</v>
       </c>
       <c r="F26" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G26" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H26" t="n">
         <v>2</v>
@@ -840,16 +841,16 @@
         <v>46014</v>
       </c>
       <c r="D27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F27" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="G27" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="H27" t="n">
         <v>2</v>
@@ -863,16 +864,16 @@
         <v>46015</v>
       </c>
       <c r="D28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F28" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G28" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="H28" t="n">
         <v>2</v>
@@ -892,10 +893,10 @@
         <v>0</v>
       </c>
       <c r="F29" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G29" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="H29" t="n">
         <v>2</v>
@@ -909,19 +910,19 @@
         <v>46017</v>
       </c>
       <c r="D30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E30" t="n">
         <v>1</v>
       </c>
       <c r="F30" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G30" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="H30" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="31">
@@ -932,19 +933,19 @@
         <v>46020</v>
       </c>
       <c r="D31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F31" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G31" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="H31" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="32">
@@ -961,13 +962,13 @@
         <v>1</v>
       </c>
       <c r="F32" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G32" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="H32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="33">
@@ -978,16 +979,16 @@
         <v>46022</v>
       </c>
       <c r="D33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E33" t="n">
         <v>0</v>
       </c>
       <c r="F33" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="G33" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="H33" t="n">
         <v>1</v>
@@ -1004,16 +1005,16 @@
         <v>0</v>
       </c>
       <c r="E34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F34" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="G34" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="H34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="35">
@@ -1024,19 +1025,19 @@
         <v>46024</v>
       </c>
       <c r="D35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F35" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G35" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="H35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="36">
@@ -1047,7 +1048,7 @@
         <v>46027</v>
       </c>
       <c r="D36" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E36" t="n">
         <v>0</v>
@@ -1056,10 +1057,10 @@
         <v>11</v>
       </c>
       <c r="G36" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="H36" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="37">
@@ -1073,16 +1074,16 @@
         <v>0</v>
       </c>
       <c r="E37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F37" t="n">
         <v>11</v>
       </c>
       <c r="G37" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H37" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="38">
@@ -1093,19 +1094,19 @@
         <v>46029</v>
       </c>
       <c r="D38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E38" t="n">
         <v>0</v>
       </c>
       <c r="F38" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G38" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H38" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="39">
@@ -1116,19 +1117,19 @@
         <v>46030</v>
       </c>
       <c r="D39" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E39" t="n">
         <v>0</v>
       </c>
       <c r="F39" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G39" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H39" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="40">
@@ -1145,13 +1146,13 @@
         <v>0</v>
       </c>
       <c r="F40" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G40" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H40" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="41">
@@ -1162,19 +1163,19 @@
         <v>46034</v>
       </c>
       <c r="D41" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F41" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G41" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="H41" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="42">
@@ -1191,13 +1192,13 @@
         <v>0</v>
       </c>
       <c r="F42" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G42" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="H42" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="43">
@@ -1214,13 +1215,13 @@
         <v>1</v>
       </c>
       <c r="F43" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G43" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H43" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="44">
@@ -1231,19 +1232,19 @@
         <v>46037</v>
       </c>
       <c r="D44" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E44" t="n">
         <v>1</v>
       </c>
       <c r="F44" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="G44" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="H44" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="45">
@@ -1254,19 +1255,19 @@
         <v>46038</v>
       </c>
       <c r="D45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F45" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="G45" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H45" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="46">
@@ -1277,19 +1278,19 @@
         <v>46041</v>
       </c>
       <c r="D46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F46" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="G46" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H46" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="47">
@@ -1300,19 +1301,19 @@
         <v>46042</v>
       </c>
       <c r="D47" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F47" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="G47" t="n">
         <v>14</v>
       </c>
       <c r="H47" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="48">
@@ -1329,13 +1330,13 @@
         <v>1</v>
       </c>
       <c r="F48" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="G48" t="n">
         <v>15</v>
       </c>
       <c r="H48" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="49">
@@ -1346,19 +1347,19 @@
         <v>46044</v>
       </c>
       <c r="D49" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E49" t="n">
         <v>0</v>
       </c>
       <c r="F49" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="G49" t="n">
         <v>15</v>
       </c>
       <c r="H49" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="50">
@@ -1369,19 +1370,19 @@
         <v>46045</v>
       </c>
       <c r="D50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E50" t="n">
         <v>0</v>
       </c>
       <c r="F50" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="G50" t="n">
         <v>15</v>
       </c>
       <c r="H50" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="51">
@@ -1392,19 +1393,19 @@
         <v>46048</v>
       </c>
       <c r="D51" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E51" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F51" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G51" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H51" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="52">
@@ -1421,13 +1422,13 @@
         <v>1</v>
       </c>
       <c r="F52" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G52" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H52" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="53">
@@ -1438,19 +1439,19 @@
         <v>46050</v>
       </c>
       <c r="D53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E53" t="n">
         <v>1</v>
       </c>
       <c r="F53" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="G53" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H53" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="54">
@@ -1464,16 +1465,16 @@
         <v>1</v>
       </c>
       <c r="E54" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F54" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="G54" t="n">
         <v>18</v>
       </c>
       <c r="H54" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="55">
@@ -1484,19 +1485,19 @@
         <v>46052</v>
       </c>
       <c r="D55" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E55" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F55" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="G55" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H55" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="56">
@@ -1507,16 +1508,16 @@
         <v>46055</v>
       </c>
       <c r="D56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E56" t="n">
         <v>0</v>
       </c>
       <c r="F56" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G56" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H56" t="n">
         <v>5</v>
@@ -1536,10 +1537,10 @@
         <v>1</v>
       </c>
       <c r="F57" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G57" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H57" t="n">
         <v>6</v>
@@ -1553,19 +1554,19 @@
         <v>46057</v>
       </c>
       <c r="D58" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E58" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F58" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="G58" t="n">
         <v>20</v>
       </c>
       <c r="H58" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="59">
@@ -1579,16 +1580,16 @@
         <v>0</v>
       </c>
       <c r="E59" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F59" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="G59" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H59" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="60">
@@ -1599,19 +1600,19 @@
         <v>46059</v>
       </c>
       <c r="D60" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E60" t="n">
         <v>1</v>
       </c>
       <c r="F60" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G60" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="H60" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="61">
@@ -1628,13 +1629,13 @@
         <v>1</v>
       </c>
       <c r="F61" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G61" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H61" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="62">
@@ -1645,19 +1646,19 @@
         <v>46063</v>
       </c>
       <c r="D62" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E62" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F62" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="G62" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="H62" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="63">
@@ -1674,13 +1675,13 @@
         <v>1</v>
       </c>
       <c r="F63" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="G63" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="H63" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="64">
@@ -1694,16 +1695,16 @@
         <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F64" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="G64" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H64" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="65">
@@ -1720,13 +1721,13 @@
         <v>0</v>
       </c>
       <c r="F65" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="G65" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H65" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="66">
@@ -1737,19 +1738,19 @@
         <v>46069</v>
       </c>
       <c r="D66" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E66" t="n">
         <v>1</v>
       </c>
       <c r="F66" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="G66" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H66" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="67">
@@ -1760,19 +1761,19 @@
         <v>46070</v>
       </c>
       <c r="D67" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E67" t="n">
         <v>1</v>
       </c>
       <c r="F67" t="n">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="G67" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H67" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="68">
@@ -1789,13 +1790,13 @@
         <v>0</v>
       </c>
       <c r="F68" t="n">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="G68" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H68" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="69">
@@ -1806,19 +1807,19 @@
         <v>46072</v>
       </c>
       <c r="D69" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E69" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F69" t="n">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="G69" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="H69" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="70">
@@ -1835,13 +1836,13 @@
         <v>0</v>
       </c>
       <c r="F70" t="n">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="G70" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="H70" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="71">
@@ -1855,16 +1856,16 @@
         <v>0</v>
       </c>
       <c r="E71" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F71" t="n">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="G71" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="H71" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="72">
@@ -1881,13 +1882,13 @@
         <v>0</v>
       </c>
       <c r="F72" t="n">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="G72" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="H72" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="73">
@@ -1904,13 +1905,13 @@
         <v>1</v>
       </c>
       <c r="F73" t="n">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="G73" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="H73" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="74">
@@ -1927,13 +1928,13 @@
         <v>0</v>
       </c>
       <c r="F74" t="n">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="G74" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="H74" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="75">
@@ -1950,13 +1951,13 @@
         <v>0</v>
       </c>
       <c r="F75" t="n">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="G75" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="H75" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="76">
@@ -1973,13 +1974,13 @@
         <v>0</v>
       </c>
       <c r="F76" t="n">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="G76" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="H76" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="77">
@@ -1996,13 +1997,13 @@
         <v>0</v>
       </c>
       <c r="F77" t="n">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="G77" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="H77" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="78">
@@ -2019,13 +2020,13 @@
         <v>0</v>
       </c>
       <c r="F78" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="G78" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="H78" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="79">
@@ -2042,13 +2043,13 @@
         <v>0</v>
       </c>
       <c r="F79" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="G79" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="H79" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -2190,68 +2191,68 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>欠陥1: 03_請求の不具合</t>
+          <t>欠陥1: 05_清算の不具合</t>
         </is>
       </c>
       <c r="D9" s="2" t="n">
-        <v>46047</v>
+        <v>46060</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>02_受付</t>
+          <t>03_請求</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
           <t>中</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>高</t>
-        </is>
-      </c>
       <c r="O9" s="2" t="n">
-        <v>46049</v>
+        <v>46064</v>
       </c>
       <c r="P9" s="2" t="n">
-        <v>46051</v>
+        <v>46063</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>プロセス不備</t>
+          <t>外的要因</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>その他</t>
+          <t>RD</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>非欠陥</t>
-        </is>
+          <t>ITa</t>
+        </is>
+      </c>
+      <c r="AC9" s="3" t="n">
+        <v>46069</v>
       </c>
       <c r="AD9" s="2" t="n">
-        <v>46059</v>
-      </c>
-      <c r="AE9" s="2" t="n">
-        <v>46057</v>
-      </c>
-      <c r="AG9" t="inlineStr">
+        <v>46074</v>
+      </c>
+      <c r="AF9" t="inlineStr">
         <is>
           <t>無</t>
         </is>
       </c>
-      <c r="AH9" t="inlineStr"/>
+      <c r="AG9" t="inlineStr"/>
       <c r="AK9" s="2" t="n">
-        <v>46064</v>
+        <v>46074</v>
       </c>
       <c r="AL9" s="2" t="n">
-        <v>46064</v>
+        <v>46076</v>
       </c>
       <c r="AM9" s="2" t="n">
-        <v>46059</v>
+        <v>46078</v>
       </c>
       <c r="AP9" t="n">
         <v>1</v>
@@ -2270,32 +2271,32 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>欠陥2: 02_受付の不具合</t>
+          <t>欠陥2: 30_運用の不具合</t>
         </is>
       </c>
       <c r="D10" s="2" t="n">
-        <v>46011</v>
+        <v>46068</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>06_受入準備</t>
+          <t>01_委託者登録</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
           <t>中</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>高</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="n">
-        <v>46016</v>
+        <v>46073</v>
       </c>
       <c r="P10" s="2" t="n">
-        <v>46015</v>
+        <v>46073</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -2304,7 +2305,7 @@
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>ED</t>
+          <t>その他</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -2312,26 +2313,36 @@
           <t>CT</t>
         </is>
       </c>
+      <c r="AC10" s="3" t="n">
+        <v>46080</v>
+      </c>
       <c r="AD10" s="2" t="n">
-        <v>46019</v>
-      </c>
-      <c r="AE10" s="2" t="n">
-        <v>46017</v>
+        <v>46082</v>
+      </c>
+      <c r="AF10" t="inlineStr">
+        <is>
+          <t>有</t>
+        </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>無</t>
-        </is>
-      </c>
-      <c r="AH10" t="inlineStr"/>
+          <t>20_移行</t>
+        </is>
+      </c>
+      <c r="AH10" s="3" t="n">
+        <v>46085</v>
+      </c>
+      <c r="AI10" s="2" t="n">
+        <v>46087</v>
+      </c>
       <c r="AK10" s="2" t="n">
-        <v>46025</v>
+        <v>46086</v>
       </c>
       <c r="AL10" s="2" t="n">
-        <v>46028</v>
+        <v>46086</v>
       </c>
       <c r="AM10" s="2" t="n">
-        <v>46021</v>
+        <v>46085</v>
       </c>
       <c r="AP10" t="n">
         <v>1</v>
@@ -2350,11 +2361,11 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>欠陥3: 10_共通の不具合</t>
+          <t>欠陥3: 06_受入準備の不具合</t>
         </is>
       </c>
       <c r="D11" s="2" t="n">
-        <v>46017</v>
+        <v>46048</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -2368,18 +2379,18 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>高</t>
+          <t>低</t>
         </is>
       </c>
       <c r="O11" s="2" t="n">
-        <v>46022</v>
+        <v>46050</v>
       </c>
       <c r="P11" s="2" t="n">
-        <v>46021</v>
+        <v>46049</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>考慮不足</t>
+          <t>未知</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
@@ -2389,29 +2400,39 @@
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>CT</t>
-        </is>
+          <t>ITa</t>
+        </is>
+      </c>
+      <c r="AC11" s="3" t="n">
+        <v>46059</v>
       </c>
       <c r="AD11" s="2" t="n">
-        <v>46029</v>
-      </c>
-      <c r="AE11" s="2" t="n">
-        <v>46033</v>
+        <v>46058</v>
+      </c>
+      <c r="AF11" t="inlineStr">
+        <is>
+          <t>有</t>
+        </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>無</t>
-        </is>
-      </c>
-      <c r="AH11" t="inlineStr"/>
+          <t>10_共通</t>
+        </is>
+      </c>
+      <c r="AH11" s="3" t="n">
+        <v>46064</v>
+      </c>
+      <c r="AI11" s="2" t="n">
+        <v>46066</v>
+      </c>
       <c r="AK11" s="2" t="n">
-        <v>46037</v>
+        <v>46071</v>
       </c>
       <c r="AL11" s="2" t="n">
-        <v>46038</v>
+        <v>46073</v>
       </c>
       <c r="AM11" s="2" t="n">
-        <v>46038</v>
+        <v>46063</v>
       </c>
       <c r="AP11" t="n">
         <v>1</v>
@@ -2430,15 +2451,15 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>欠陥4: 05_清算の不具合</t>
+          <t>欠陥4: 20_移行の不具合</t>
         </is>
       </c>
       <c r="D12" s="2" t="n">
-        <v>46059</v>
+        <v>46004</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>01_委託者登録</t>
+          <t>20_移行</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -2448,50 +2469,60 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>低</t>
+          <t>高</t>
         </is>
       </c>
       <c r="O12" s="2" t="n">
-        <v>46062</v>
+        <v>46008</v>
       </c>
       <c r="P12" s="2" t="n">
-        <v>46064</v>
+        <v>46010</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>技術力不足</t>
+          <t>プロセス不備</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>RD</t>
+          <t>PD</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>非欠陥</t>
-        </is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="AC12" s="3" t="n">
+        <v>46011</v>
       </c>
       <c r="AD12" s="2" t="n">
-        <v>46070</v>
-      </c>
-      <c r="AE12" s="2" t="n">
-        <v>46075</v>
+        <v>46013</v>
+      </c>
+      <c r="AF12" t="inlineStr">
+        <is>
+          <t>有</t>
+        </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>無</t>
-        </is>
-      </c>
-      <c r="AH12" t="inlineStr"/>
+          <t>30_運用</t>
+        </is>
+      </c>
+      <c r="AH12" s="3" t="n">
+        <v>46017</v>
+      </c>
+      <c r="AI12" s="2" t="n">
+        <v>46017</v>
+      </c>
       <c r="AK12" s="2" t="n">
-        <v>46083</v>
+        <v>46025</v>
       </c>
       <c r="AL12" s="2" t="n">
-        <v>46082</v>
+        <v>46026</v>
       </c>
       <c r="AM12" s="2" t="n">
-        <v>46077</v>
+        <v>46015</v>
       </c>
       <c r="AP12" t="n">
         <v>1</v>
@@ -2510,15 +2541,15 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>欠陥5: 05_清算の不具合</t>
+          <t>欠陥5: 03_請求の不具合</t>
         </is>
       </c>
       <c r="D13" s="2" t="n">
-        <v>46005</v>
+        <v>46044</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>03_請求</t>
+          <t>04_欠陥・返戻</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -2528,18 +2559,18 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>低</t>
+          <t>高</t>
         </is>
       </c>
       <c r="O13" s="2" t="n">
-        <v>46007</v>
+        <v>46046</v>
       </c>
       <c r="P13" s="2" t="n">
-        <v>46007</v>
+        <v>46046</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>非欠陥</t>
+          <t>未知</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
@@ -2552,36 +2583,26 @@
           <t>CT</t>
         </is>
       </c>
+      <c r="AC13" s="3" t="n">
+        <v>46053</v>
+      </c>
       <c r="AD13" s="2" t="n">
-        <v>46010</v>
-      </c>
-      <c r="AE13" s="2" t="n">
-        <v>46015</v>
-      </c>
-      <c r="AG13" t="inlineStr">
-        <is>
-          <t>有</t>
-        </is>
-      </c>
-      <c r="AH13" t="inlineStr">
-        <is>
-          <t>20_移行</t>
-        </is>
-      </c>
-      <c r="AI13" s="2" t="n">
-        <v>46015</v>
-      </c>
-      <c r="AJ13" s="2" t="n">
-        <v>46017</v>
-      </c>
+        <v>46054</v>
+      </c>
+      <c r="AF13" t="inlineStr">
+        <is>
+          <t>無</t>
+        </is>
+      </c>
+      <c r="AG13" t="inlineStr"/>
       <c r="AK13" s="2" t="n">
-        <v>46022</v>
+        <v>46063</v>
       </c>
       <c r="AL13" s="2" t="n">
-        <v>46021</v>
+        <v>46065</v>
       </c>
       <c r="AM13" s="2" t="n">
-        <v>46017</v>
+        <v>46055</v>
       </c>
       <c r="AP13" t="n">
         <v>1</v>
@@ -2600,69 +2621,62 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>欠陥6: 40_基盤の不具合</t>
+          <t>欠陥6: 20_移行の不具合</t>
         </is>
       </c>
       <c r="D14" s="2" t="n">
+        <v>46023</v>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>30_運用</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="n">
+        <v>46025</v>
+      </c>
+      <c r="P14" s="2" t="n">
+        <v>46027</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>業務/仕様理解不足</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>ED</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>ITa</t>
+        </is>
+      </c>
+      <c r="AC14" s="3" t="n">
         <v>46028</v>
       </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>05_清算</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>高</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>中</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="n">
-        <v>46032</v>
-      </c>
-      <c r="P14" s="2" t="n">
-        <v>46034</v>
-      </c>
-      <c r="T14" t="inlineStr">
-        <is>
-          <t>情報共有不足</t>
-        </is>
-      </c>
-      <c r="U14" t="inlineStr">
-        <is>
-          <t>非欠陥</t>
-        </is>
-      </c>
-      <c r="V14" t="inlineStr">
-        <is>
-          <t>ITb</t>
-        </is>
-      </c>
       <c r="AD14" s="2" t="n">
-        <v>46041</v>
-      </c>
-      <c r="AE14" s="2" t="n">
-        <v>46041</v>
-      </c>
-      <c r="AG14" t="inlineStr">
-        <is>
-          <t>有</t>
-        </is>
-      </c>
-      <c r="AH14" t="inlineStr">
-        <is>
-          <t>30_運用</t>
-        </is>
-      </c>
-      <c r="AI14" s="2" t="n">
-        <v>46046</v>
-      </c>
+        <v>46026</v>
+      </c>
+      <c r="AF14" t="inlineStr">
+        <is>
+          <t>無</t>
+        </is>
+      </c>
+      <c r="AG14" t="inlineStr"/>
       <c r="AK14" s="2" t="n">
-        <v>46052</v>
+        <v>46037</v>
       </c>
       <c r="AP14" t="n">
         <v>1</v>
@@ -2681,11 +2695,11 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>欠陥7: 06_受入準備の不具合</t>
+          <t>欠陥7: 10_共通の不具合</t>
         </is>
       </c>
       <c r="D15" s="2" t="n">
-        <v>46009</v>
+        <v>46010</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -2694,7 +2708,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>低</t>
+          <t>高</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
@@ -2710,40 +2724,33 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>プロセス不備</t>
+          <t>業務/仕様理解不足</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>その他</t>
+          <t>ID</t>
         </is>
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>ITb</t>
-        </is>
+          <t>非欠陥</t>
+        </is>
+      </c>
+      <c r="AC15" s="3" t="n">
+        <v>46017</v>
       </c>
       <c r="AD15" s="2" t="n">
-        <v>46023</v>
-      </c>
-      <c r="AE15" s="2" t="n">
-        <v>46026</v>
-      </c>
-      <c r="AG15" t="inlineStr">
-        <is>
-          <t>有</t>
-        </is>
-      </c>
-      <c r="AH15" t="inlineStr">
-        <is>
-          <t>30_運用</t>
-        </is>
-      </c>
-      <c r="AI15" s="2" t="n">
-        <v>46029</v>
-      </c>
+        <v>46022</v>
+      </c>
+      <c r="AF15" t="inlineStr">
+        <is>
+          <t>無</t>
+        </is>
+      </c>
+      <c r="AG15" t="inlineStr"/>
       <c r="AK15" s="2" t="n">
-        <v>46034</v>
+        <v>46025</v>
       </c>
       <c r="AP15" t="n">
         <v>1</v>
@@ -2762,62 +2769,62 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>欠陥8: 40_基盤の不具合</t>
+          <t>欠陥8: 20_移行の不具合</t>
         </is>
       </c>
       <c r="D16" s="2" t="n">
-        <v>46079</v>
+        <v>45998</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>08_事務支(変更通知)</t>
+          <t>03_請求</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
           <t>低</t>
         </is>
       </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>低</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="n">
-        <v>46081</v>
+        <v>46000</v>
       </c>
       <c r="P16" s="2" t="n">
-        <v>46080</v>
+        <v>46002</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>注意不足</t>
+          <t>プロセス不備</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>非欠陥</t>
+          <t>RD</t>
         </is>
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>ITa</t>
-        </is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="AC16" s="3" t="n">
+        <v>46004</v>
       </c>
       <c r="AD16" s="2" t="n">
-        <v>46088</v>
-      </c>
-      <c r="AE16" s="2" t="n">
-        <v>46089</v>
-      </c>
-      <c r="AG16" t="inlineStr">
+        <v>46004</v>
+      </c>
+      <c r="AF16" t="inlineStr">
         <is>
           <t>無</t>
         </is>
       </c>
-      <c r="AH16" t="inlineStr"/>
+      <c r="AG16" t="inlineStr"/>
       <c r="AK16" s="2" t="n">
-        <v>46093</v>
+        <v>46014</v>
       </c>
       <c r="AP16" t="n">
         <v>1</v>
@@ -2836,59 +2843,59 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>欠陥9: 40_基盤の不具合</t>
+          <t>欠陥9: 06_受入準備の不具合</t>
         </is>
       </c>
       <c r="D17" s="2" t="n">
-        <v>45998</v>
+        <v>46033</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>06_受入準備</t>
+          <t>20_移行</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
           <t>中</t>
         </is>
       </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>低</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="n">
-        <v>46002</v>
+        <v>46038</v>
       </c>
       <c r="P17" s="2" t="n">
-        <v>46002</v>
+        <v>46037</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>影響範囲調査不足</t>
+          <t>未知</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>ID</t>
+          <t>RD</t>
         </is>
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>ITb</t>
-        </is>
-      </c>
-      <c r="AD17" s="2" t="n">
-        <v>46006</v>
-      </c>
-      <c r="AG17" t="inlineStr">
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="AC17" s="3" t="n">
+        <v>46046</v>
+      </c>
+      <c r="AF17" t="inlineStr">
         <is>
           <t>無</t>
         </is>
       </c>
-      <c r="AH17" t="inlineStr"/>
+      <c r="AG17" t="inlineStr"/>
       <c r="AK17" s="2" t="n">
-        <v>46014</v>
+        <v>46058</v>
       </c>
       <c r="AP17" t="n">
         <v>1</v>
@@ -2907,59 +2914,59 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>欠陥10: 02_受付の不具合</t>
+          <t>欠陥10: 03_請求の不具合</t>
         </is>
       </c>
       <c r="D18" s="2" t="n">
-        <v>46062</v>
+        <v>46071</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>06_受入準備</t>
+          <t>01_委託者登録</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
           <t>中</t>
         </is>
       </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>高</t>
-        </is>
-      </c>
       <c r="O18" s="2" t="n">
-        <v>46072</v>
+        <v>46024</v>
       </c>
       <c r="P18" s="2" t="n">
-        <v>46075</v>
+        <v>46026</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
           <t>非欠陥</t>
         </is>
       </c>
-      <c r="U18" t="inlineStr">
-        <is>
-          <t>非欠陥</t>
-        </is>
-      </c>
       <c r="V18" t="inlineStr">
         <is>
           <t>ST</t>
         </is>
       </c>
-      <c r="AD18" s="2" t="n">
-        <v>46076</v>
-      </c>
-      <c r="AG18" t="inlineStr">
+      <c r="AC18" s="3" t="n">
+        <v>46031</v>
+      </c>
+      <c r="AF18" t="inlineStr">
         <is>
           <t>無</t>
         </is>
       </c>
-      <c r="AH18" t="inlineStr"/>
+      <c r="AG18" t="inlineStr"/>
       <c r="AK18" s="2" t="n">
-        <v>46085</v>
+        <v>46039</v>
       </c>
       <c r="AP18" t="n">
         <v>1</v>
@@ -2978,20 +2985,20 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>欠陥11: 03_請求の不具合</t>
+          <t>欠陥11: 08_事務支(変更通知)の不具合</t>
         </is>
       </c>
       <c r="D19" s="2" t="n">
-        <v>46011</v>
+        <v>46069</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>06_受入準備</t>
+          <t>20_移行</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>中</t>
+          <t>低</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -3000,34 +3007,34 @@
         </is>
       </c>
       <c r="O19" s="2" t="n">
-        <v>46014</v>
+        <v>46074</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>業務/仕様理解不足</t>
+          <t>注意不足</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>PD</t>
+          <t>ED</t>
         </is>
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>非欠陥</t>
-        </is>
-      </c>
-      <c r="AD19" s="2" t="n">
-        <v>46018</v>
-      </c>
-      <c r="AG19" t="inlineStr">
+          <t>ITa</t>
+        </is>
+      </c>
+      <c r="AC19" s="3" t="n">
+        <v>46082</v>
+      </c>
+      <c r="AF19" t="inlineStr">
         <is>
           <t>無</t>
         </is>
       </c>
-      <c r="AH19" t="inlineStr"/>
+      <c r="AG19" t="inlineStr"/>
       <c r="AK19" s="2" t="n">
-        <v>46031</v>
+        <v>46087</v>
       </c>
       <c r="AP19" t="n">
         <v>1</v>
@@ -3046,33 +3053,33 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>欠陥12: 30_運用の不具合</t>
+          <t>欠陥12: 05_清算の不具合</t>
         </is>
       </c>
       <c r="D20" s="2" t="n">
-        <v>46066</v>
+        <v>46005</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>20_移行</t>
+          <t>10_共通</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>低</t>
+          <t>高</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>高</t>
+          <t>中</t>
         </is>
       </c>
       <c r="O20" s="2" t="n">
-        <v>46071</v>
+        <v>46010</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>未知</t>
+          <t>外的要因</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
@@ -3082,20 +3089,27 @@
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>非欠陥</t>
-        </is>
-      </c>
-      <c r="AD20" s="2" t="n">
-        <v>46078</v>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="AC20" s="3" t="n">
+        <v>46015</v>
+      </c>
+      <c r="AF20" t="inlineStr">
+        <is>
+          <t>有</t>
+        </is>
       </c>
       <c r="AG20" t="inlineStr">
         <is>
-          <t>無</t>
-        </is>
-      </c>
-      <c r="AH20" t="inlineStr"/>
+          <t>03_請求</t>
+        </is>
+      </c>
+      <c r="AH20" s="3" t="n">
+        <v>46021</v>
+      </c>
       <c r="AK20" s="2" t="n">
-        <v>46084</v>
+        <v>46023</v>
       </c>
       <c r="AP20" t="n">
         <v>1</v>
@@ -3114,33 +3128,33 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>欠陥13: 01_委託者登録の不具合</t>
+          <t>欠陥13: 05_清算の不具合</t>
         </is>
       </c>
       <c r="D21" s="2" t="n">
-        <v>46071</v>
+        <v>46010</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>08_事務支(変更通知)</t>
+          <t>03_請求</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>中</t>
+          <t>低</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>高</t>
+          <t>低</t>
         </is>
       </c>
       <c r="O21" s="2" t="n">
-        <v>46073</v>
+        <v>46013</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>未知</t>
+          <t>考慮不足</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
@@ -3150,20 +3164,20 @@
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>非欠陥</t>
-        </is>
-      </c>
-      <c r="AD21" s="2" t="n">
-        <v>46076</v>
-      </c>
-      <c r="AG21" t="inlineStr">
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="AC21" s="3" t="n">
+        <v>46023</v>
+      </c>
+      <c r="AF21" t="inlineStr">
         <is>
           <t>無</t>
         </is>
       </c>
-      <c r="AH21" t="inlineStr"/>
+      <c r="AG21" t="inlineStr"/>
       <c r="AK21" s="2" t="n">
-        <v>46081</v>
+        <v>46030</v>
       </c>
       <c r="AP21" t="n">
         <v>1</v>
@@ -3182,20 +3196,20 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>欠陥14: 40_基盤の不具合</t>
+          <t>欠陥14: 10_共通の不具合</t>
         </is>
       </c>
       <c r="D22" s="2" t="n">
-        <v>46003</v>
+        <v>46049</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>08_事務支(変更通知)</t>
+          <t>04_欠陥・返戻</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>中</t>
+          <t>低</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
@@ -3204,34 +3218,34 @@
         </is>
       </c>
       <c r="O22" s="2" t="n">
-        <v>46006</v>
+        <v>46054</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>注意不足</t>
+          <t>影響範囲調査不足</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>PD</t>
+          <t>RD</t>
         </is>
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>ST</t>
-        </is>
-      </c>
-      <c r="AD22" s="2" t="n">
-        <v>46009</v>
-      </c>
-      <c r="AG22" t="inlineStr">
+          <t>CT</t>
+        </is>
+      </c>
+      <c r="AC22" s="3" t="n">
+        <v>46064</v>
+      </c>
+      <c r="AF22" t="inlineStr">
         <is>
           <t>無</t>
         </is>
       </c>
-      <c r="AH22" t="inlineStr"/>
+      <c r="AG22" t="inlineStr"/>
       <c r="AK22" s="2" t="n">
-        <v>46016</v>
+        <v>46069</v>
       </c>
       <c r="AP22" t="n">
         <v>1</v>
@@ -3250,7 +3264,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>欠陥15: 03_請求の不具合</t>
+          <t>欠陥15: 09_事務支(その他)の不具合</t>
         </is>
       </c>
       <c r="D23" s="2" t="n">
@@ -3258,7 +3272,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>07_口振契約受付</t>
+          <t>01_委託者登録</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -3268,7 +3282,7 @@
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>高</t>
+          <t>低</t>
         </is>
       </c>
       <c r="O23" s="2" t="n">
@@ -3276,7 +3290,7 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>考慮不足</t>
+          <t>業務/仕様理解不足</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
@@ -3286,20 +3300,27 @@
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>CT</t>
-        </is>
-      </c>
-      <c r="AD23" s="2" t="n">
-        <v>46040</v>
+          <t>ITb</t>
+        </is>
+      </c>
+      <c r="AC23" s="3" t="n">
+        <v>46044</v>
+      </c>
+      <c r="AF23" t="inlineStr">
+        <is>
+          <t>有</t>
+        </is>
       </c>
       <c r="AG23" t="inlineStr">
         <is>
-          <t>無</t>
-        </is>
-      </c>
-      <c r="AH23" t="inlineStr"/>
+          <t>04_欠陥・返戻</t>
+        </is>
+      </c>
+      <c r="AH23" s="3" t="n">
+        <v>46048</v>
+      </c>
       <c r="AK23" s="2" t="n">
-        <v>46046</v>
+        <v>46051</v>
       </c>
       <c r="AP23" t="n">
         <v>1</v>
@@ -3318,33 +3339,33 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>欠陥16: 07_口振契約受付の不具合</t>
+          <t>欠陥16: 01_委託者登録の不具合</t>
         </is>
       </c>
       <c r="D24" s="2" t="n">
-        <v>45998</v>
+        <v>46061</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>20_移行</t>
+          <t>03_請求</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
           <t>高</t>
         </is>
       </c>
-      <c r="N24" t="inlineStr">
-        <is>
-          <t>低</t>
-        </is>
-      </c>
       <c r="O24" s="2" t="n">
-        <v>45999</v>
+        <v>46062</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>注意不足</t>
+          <t>業務/仕様理解不足</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
@@ -3354,27 +3375,27 @@
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>ITa</t>
-        </is>
-      </c>
-      <c r="AD24" s="2" t="n">
-        <v>46003</v>
+          <t>CT</t>
+        </is>
+      </c>
+      <c r="AC24" s="3" t="n">
+        <v>46065</v>
+      </c>
+      <c r="AF24" t="inlineStr">
+        <is>
+          <t>有</t>
+        </is>
       </c>
       <c r="AG24" t="inlineStr">
         <is>
-          <t>有</t>
-        </is>
-      </c>
-      <c r="AH24" t="inlineStr">
-        <is>
-          <t>30_運用</t>
-        </is>
-      </c>
-      <c r="AI24" s="2" t="n">
-        <v>46010</v>
+          <t>03_請求</t>
+        </is>
+      </c>
+      <c r="AH24" s="3" t="n">
+        <v>46071</v>
       </c>
       <c r="AK24" s="2" t="n">
-        <v>46010</v>
+        <v>46071</v>
       </c>
       <c r="AP24" t="n">
         <v>1</v>
@@ -3393,15 +3414,15 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>欠陥17: 04_欠陥・返戻の不具合</t>
+          <t>欠陥17: 20_移行の不具合</t>
         </is>
       </c>
       <c r="D25" s="2" t="n">
-        <v>46046</v>
+        <v>46035</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>01_委託者登録</t>
+          <t>08_事務支(変更通知)</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -3415,34 +3436,34 @@
         </is>
       </c>
       <c r="O25" s="2" t="n">
-        <v>46047</v>
+        <v>46037</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>プロセス不備</t>
+          <t>情報共有不足</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>非欠陥</t>
+          <t>ED</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>ITb</t>
-        </is>
-      </c>
-      <c r="AD25" s="2" t="n">
-        <v>46050</v>
-      </c>
-      <c r="AG25" t="inlineStr">
+          <t>CT</t>
+        </is>
+      </c>
+      <c r="AC25" s="3" t="n">
+        <v>46040</v>
+      </c>
+      <c r="AF25" t="inlineStr">
         <is>
           <t>無</t>
         </is>
       </c>
-      <c r="AH25" t="inlineStr"/>
+      <c r="AG25" t="inlineStr"/>
       <c r="AK25" s="2" t="n">
-        <v>46056</v>
+        <v>46053</v>
       </c>
       <c r="AP25" t="n">
         <v>0</v>
@@ -3461,15 +3482,15 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>欠陥18: 09_事務支(その他)の不具合</t>
+          <t>欠陥18: 10_共通の不具合</t>
         </is>
       </c>
       <c r="D26" s="2" t="n">
-        <v>45996</v>
+        <v>46040</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>07_口振契約受付</t>
+          <t>05_清算</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -3479,20 +3500,20 @@
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>高</t>
+          <t>低</t>
         </is>
       </c>
       <c r="O26" s="2" t="n">
-        <v>46000</v>
+        <v>46044</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>外的要因</t>
+          <t>考慮不足</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
         <is>
-          <t>ID</t>
+          <t>PD</t>
         </is>
       </c>
       <c r="V26" t="inlineStr">
@@ -3500,24 +3521,17 @@
           <t>ST</t>
         </is>
       </c>
-      <c r="AD26" s="2" t="n">
-        <v>46008</v>
-      </c>
-      <c r="AG26" t="inlineStr">
-        <is>
-          <t>有</t>
-        </is>
-      </c>
-      <c r="AH26" t="inlineStr">
-        <is>
-          <t>02_受付</t>
-        </is>
-      </c>
-      <c r="AI26" s="2" t="n">
-        <v>46012</v>
-      </c>
+      <c r="AC26" s="3" t="n">
+        <v>46050</v>
+      </c>
+      <c r="AF26" t="inlineStr">
+        <is>
+          <t>無</t>
+        </is>
+      </c>
+      <c r="AG26" t="inlineStr"/>
       <c r="AK26" s="2" t="n">
-        <v>46016</v>
+        <v>46059</v>
       </c>
       <c r="AP26" t="n">
         <v>0</v>
